--- a/data/nzd0091/nzd0091.xlsx
+++ b/data/nzd0091/nzd0091.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K320"/>
+  <dimension ref="A1:K321"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12902,6 +12902,45 @@
       <c r="K320" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:11:19+00:00</t>
+        </is>
+      </c>
+      <c r="B321" t="n">
+        <v>312.11</v>
+      </c>
+      <c r="C321" t="n">
+        <v>284.58</v>
+      </c>
+      <c r="D321" t="n">
+        <v>286.13</v>
+      </c>
+      <c r="E321" t="n">
+        <v>281.55</v>
+      </c>
+      <c r="F321" t="n">
+        <v>288.88</v>
+      </c>
+      <c r="G321" t="n">
+        <v>297.3</v>
+      </c>
+      <c r="H321" t="n">
+        <v>301.37</v>
+      </c>
+      <c r="I321" t="n">
+        <v>304.35</v>
+      </c>
+      <c r="J321" t="n">
+        <v>306.77</v>
+      </c>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -12916,7 +12955,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B326"/>
+  <dimension ref="A1:B327"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16179,6 +16218,16 @@
       </c>
       <c r="B326" t="n">
         <v>-0.46</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B327" t="n">
+        <v>0.59</v>
       </c>
     </row>
   </sheetData>
@@ -16347,28 +16396,28 @@
         <v>0.0961</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1106635870723361</v>
+        <v>0.1106088918046644</v>
       </c>
       <c r="J2" t="n">
+        <v>320</v>
+      </c>
+      <c r="K2" t="n">
         <v>319</v>
       </c>
-      <c r="K2" t="n">
-        <v>318</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.01814296226758572</v>
+        <v>0.01825694164754754</v>
       </c>
       <c r="M2" t="n">
-        <v>4.54371831183087</v>
+        <v>4.529734826375658</v>
       </c>
       <c r="N2" t="n">
-        <v>34.14983743618448</v>
+        <v>34.04280558666169</v>
       </c>
       <c r="O2" t="n">
-        <v>5.843786224374099</v>
+        <v>5.834621289052246</v>
       </c>
       <c r="P2" t="n">
-        <v>309.2302097678009</v>
+        <v>309.2308150434512</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -16425,28 +16474,28 @@
         <v>0.0571</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2137799189591766</v>
+        <v>0.2115967220841754</v>
       </c>
       <c r="J3" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K3" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06738574475655756</v>
+        <v>0.0665001800251237</v>
       </c>
       <c r="M3" t="n">
-        <v>4.4345718895714</v>
+        <v>4.428791107653482</v>
       </c>
       <c r="N3" t="n">
-        <v>32.50671032650314</v>
+        <v>32.43835277966136</v>
       </c>
       <c r="O3" t="n">
-        <v>5.701465629687084</v>
+        <v>5.695467740200217</v>
       </c>
       <c r="P3" t="n">
-        <v>282.134025930673</v>
+        <v>282.1582008482472</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -16503,28 +16552,28 @@
         <v>0.07140000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2535846551232945</v>
+        <v>0.2519383086534975</v>
       </c>
       <c r="J4" t="n">
+        <v>320</v>
+      </c>
+      <c r="K4" t="n">
         <v>319</v>
       </c>
-      <c r="K4" t="n">
-        <v>318</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.07428731413699607</v>
+        <v>0.07387092792069239</v>
       </c>
       <c r="M4" t="n">
-        <v>5.037771223017045</v>
+        <v>5.02999875422836</v>
       </c>
       <c r="N4" t="n">
-        <v>40.75401984977541</v>
+        <v>40.64486749361023</v>
       </c>
       <c r="O4" t="n">
-        <v>6.38388751857169</v>
+        <v>6.375332735913493</v>
       </c>
       <c r="P4" t="n">
-        <v>281.7950370138656</v>
+        <v>281.8133917266202</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -16581,28 +16630,28 @@
         <v>0.09660000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1879866685060654</v>
+        <v>0.186463743562491</v>
       </c>
       <c r="J5" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K5" t="n">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03791753948704257</v>
+        <v>0.03758297229212237</v>
       </c>
       <c r="M5" t="n">
-        <v>5.385406551088619</v>
+        <v>5.378184708317304</v>
       </c>
       <c r="N5" t="n">
-        <v>45.58112772201131</v>
+        <v>45.45371398146419</v>
       </c>
       <c r="O5" t="n">
-        <v>6.751379690256749</v>
+        <v>6.741936960656351</v>
       </c>
       <c r="P5" t="n">
-        <v>278.7773059901249</v>
+        <v>278.7943092135404</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -16659,28 +16708,28 @@
         <v>0.09760000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1379665286463752</v>
+        <v>0.1396912285329531</v>
       </c>
       <c r="J6" t="n">
+        <v>320</v>
+      </c>
+      <c r="K6" t="n">
         <v>319</v>
       </c>
-      <c r="K6" t="n">
-        <v>318</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.02406643989495139</v>
+        <v>0.02482327917573091</v>
       </c>
       <c r="M6" t="n">
-        <v>4.888362682453312</v>
+        <v>4.87881400999258</v>
       </c>
       <c r="N6" t="n">
-        <v>39.25715569595204</v>
+        <v>39.1545085780626</v>
       </c>
       <c r="O6" t="n">
-        <v>6.265553103753255</v>
+        <v>6.257356356965984</v>
       </c>
       <c r="P6" t="n">
-        <v>282.6184543625146</v>
+        <v>282.5992261067452</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -16737,28 +16786,28 @@
         <v>0.1221</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1137996811865373</v>
+        <v>0.1128910376943302</v>
       </c>
       <c r="J7" t="n">
+        <v>320</v>
+      </c>
+      <c r="K7" t="n">
         <v>319</v>
       </c>
-      <c r="K7" t="n">
-        <v>318</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.01796919134451946</v>
+        <v>0.01781496328455756</v>
       </c>
       <c r="M7" t="n">
-        <v>4.699101829186378</v>
+        <v>4.688579248346998</v>
       </c>
       <c r="N7" t="n">
-        <v>35.9949541141459</v>
+        <v>35.8877839910541</v>
       </c>
       <c r="O7" t="n">
-        <v>5.999579494776771</v>
+        <v>5.990641367253935</v>
       </c>
       <c r="P7" t="n">
-        <v>295.6090741063053</v>
+        <v>295.6192043496058</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -16815,28 +16864,28 @@
         <v>0.1491</v>
       </c>
       <c r="I8" t="n">
-        <v>0.09923914710806271</v>
+        <v>0.1000566656078103</v>
       </c>
       <c r="J8" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K8" t="n">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01150864326227363</v>
+        <v>0.01178147766691129</v>
       </c>
       <c r="M8" t="n">
-        <v>5.344263708488276</v>
+        <v>5.331253854726874</v>
       </c>
       <c r="N8" t="n">
-        <v>43.12818359259776</v>
+        <v>42.99716448488849</v>
       </c>
       <c r="O8" t="n">
-        <v>6.567205158406257</v>
+        <v>6.557222314737277</v>
       </c>
       <c r="P8" t="n">
-        <v>297.4957692369541</v>
+        <v>297.4866595381953</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -16893,28 +16942,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1887010511377082</v>
+        <v>0.1878792917160581</v>
       </c>
       <c r="J9" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K9" t="n">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04972179433846857</v>
+        <v>0.04965295058018271</v>
       </c>
       <c r="M9" t="n">
-        <v>4.562478826621732</v>
+        <v>4.552006795851972</v>
       </c>
       <c r="N9" t="n">
-        <v>34.6975642088669</v>
+        <v>34.5931043749238</v>
       </c>
       <c r="O9" t="n">
-        <v>5.890463836479</v>
+        <v>5.88159029301802</v>
       </c>
       <c r="P9" t="n">
-        <v>300.5220888374598</v>
+        <v>300.5312457932789</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -16971,28 +17020,28 @@
         <v>0.0621</v>
       </c>
       <c r="I10" t="n">
-        <v>0.01408361873897127</v>
+        <v>0.01430858018790318</v>
       </c>
       <c r="J10" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K10" t="n">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0001337831579022453</v>
+        <v>0.0001391161995267787</v>
       </c>
       <c r="M10" t="n">
-        <v>6.491771314898644</v>
+        <v>6.472611591691011</v>
       </c>
       <c r="N10" t="n">
-        <v>75.58147174352158</v>
+        <v>75.3441427910802</v>
       </c>
       <c r="O10" t="n">
-        <v>8.69376050645068</v>
+        <v>8.680100390610709</v>
       </c>
       <c r="P10" t="n">
-        <v>306.0583231286645</v>
+        <v>306.0558163584412</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -17030,7 +17079,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K320"/>
+  <dimension ref="A1:K321"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35225,6 +35274,63 @@
         </is>
       </c>
     </row>
+    <row r="321">
+      <c r="A321" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:11:19+00:00</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>-35.56017039346537,174.50869459877893</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>-35.560713701817804,174.50793913088626</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>-35.561486910834624,174.5075569474021</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>-35.56228929197343,174.50728017194857</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>-35.56312222507762,174.5072494972571</t>
+        </is>
+      </c>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>-35.5640204096543,174.50744653128996</t>
+        </is>
+      </c>
+      <c r="H321" t="inlineStr">
+        <is>
+          <t>-35.56480588627055,174.5080547621711</t>
+        </is>
+      </c>
+      <c r="I321" t="inlineStr">
+        <is>
+          <t>-35.56541181463788,174.50885412662365</t>
+        </is>
+      </c>
+      <c r="J321" t="inlineStr">
+        <is>
+          <t>-35.565733364270024,174.50974216092436</t>
+        </is>
+      </c>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0091/nzd0091.xlsx
+++ b/data/nzd0091/nzd0091.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K321"/>
+  <dimension ref="A1:K323"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12939,6 +12939,84 @@
         <v>306.77</v>
       </c>
       <c r="K321" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:11:24+00:00</t>
+        </is>
+      </c>
+      <c r="B322" t="n">
+        <v>309.48</v>
+      </c>
+      <c r="C322" t="n">
+        <v>279.79</v>
+      </c>
+      <c r="D322" t="n">
+        <v>283.14</v>
+      </c>
+      <c r="E322" t="n">
+        <v>279.86</v>
+      </c>
+      <c r="F322" t="n">
+        <v>284.91</v>
+      </c>
+      <c r="G322" t="n">
+        <v>295.2</v>
+      </c>
+      <c r="H322" t="n">
+        <v>299.57</v>
+      </c>
+      <c r="I322" t="n">
+        <v>302.84</v>
+      </c>
+      <c r="J322" t="n">
+        <v>309.94</v>
+      </c>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B323" t="n">
+        <v>310.44</v>
+      </c>
+      <c r="C323" t="n">
+        <v>279.52</v>
+      </c>
+      <c r="D323" t="n">
+        <v>284.05</v>
+      </c>
+      <c r="E323" t="n">
+        <v>279.36</v>
+      </c>
+      <c r="F323" t="n">
+        <v>284.94</v>
+      </c>
+      <c r="G323" t="n">
+        <v>295.84</v>
+      </c>
+      <c r="H323" t="n">
+        <v>299.9</v>
+      </c>
+      <c r="I323" t="n">
+        <v>303.15</v>
+      </c>
+      <c r="J323" t="n">
+        <v>309.8</v>
+      </c>
+      <c r="K323" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -12955,7 +13033,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B327"/>
+  <dimension ref="A1:B329"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16228,6 +16306,26 @@
       </c>
       <c r="B327" t="n">
         <v>0.59</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B328" t="n">
+        <v>-0.44</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B329" t="n">
+        <v>0.48</v>
       </c>
     </row>
   </sheetData>
@@ -16396,28 +16494,28 @@
         <v>0.0961</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1106088918046644</v>
+        <v>0.1076727996840724</v>
       </c>
       <c r="J2" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="K2" t="n">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01825694164754754</v>
+        <v>0.01755174149074556</v>
       </c>
       <c r="M2" t="n">
-        <v>4.529734826375658</v>
+        <v>4.515296389732407</v>
       </c>
       <c r="N2" t="n">
-        <v>34.04280558666169</v>
+        <v>33.8626523314363</v>
       </c>
       <c r="O2" t="n">
-        <v>5.834621289052246</v>
+        <v>5.819162511172574</v>
       </c>
       <c r="P2" t="n">
-        <v>309.2308150434512</v>
+        <v>309.2633995648879</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -16474,28 +16572,28 @@
         <v>0.0571</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2115967220841754</v>
+        <v>0.2008466507015371</v>
       </c>
       <c r="J3" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="K3" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0665001800251237</v>
+        <v>0.06043093326738824</v>
       </c>
       <c r="M3" t="n">
-        <v>4.428791107653482</v>
+        <v>4.4410893805622</v>
       </c>
       <c r="N3" t="n">
-        <v>32.43835277966136</v>
+        <v>32.64434490049675</v>
       </c>
       <c r="O3" t="n">
-        <v>5.695467740200217</v>
+        <v>5.713522985032681</v>
       </c>
       <c r="P3" t="n">
-        <v>282.1582008482472</v>
+        <v>282.2775882025643</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -16552,28 +16650,28 @@
         <v>0.07140000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2519383086534975</v>
+        <v>0.2453392089904504</v>
       </c>
       <c r="J4" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="K4" t="n">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="L4" t="n">
-        <v>0.07387092792069239</v>
+        <v>0.07104053937992794</v>
       </c>
       <c r="M4" t="n">
-        <v>5.02999875422836</v>
+        <v>5.030376578971504</v>
       </c>
       <c r="N4" t="n">
-        <v>40.64486749361023</v>
+        <v>40.54407919596444</v>
       </c>
       <c r="O4" t="n">
-        <v>6.375332735913493</v>
+        <v>6.367423277587601</v>
       </c>
       <c r="P4" t="n">
-        <v>281.8133917266202</v>
+        <v>281.8871745213021</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -16630,28 +16728,28 @@
         <v>0.09660000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>0.186463743562491</v>
+        <v>0.1808971605951366</v>
       </c>
       <c r="J5" t="n">
+        <v>322</v>
+      </c>
+      <c r="K5" t="n">
         <v>320</v>
       </c>
-      <c r="K5" t="n">
-        <v>318</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.03758297229212237</v>
+        <v>0.03587502107356422</v>
       </c>
       <c r="M5" t="n">
-        <v>5.378184708317304</v>
+        <v>5.379660513938975</v>
       </c>
       <c r="N5" t="n">
-        <v>45.45371398146419</v>
+        <v>45.27759494754566</v>
       </c>
       <c r="O5" t="n">
-        <v>6.741936960656351</v>
+        <v>6.728862827220188</v>
       </c>
       <c r="P5" t="n">
-        <v>278.7943092135404</v>
+        <v>278.8566419537007</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -16708,28 +16806,28 @@
         <v>0.09760000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1396912285329531</v>
+        <v>0.1378003746626313</v>
       </c>
       <c r="J6" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="K6" t="n">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02482327917573091</v>
+        <v>0.02451426065054518</v>
       </c>
       <c r="M6" t="n">
-        <v>4.87881400999258</v>
+        <v>4.859581025602604</v>
       </c>
       <c r="N6" t="n">
-        <v>39.1545085780626</v>
+        <v>38.92296631451015</v>
       </c>
       <c r="O6" t="n">
-        <v>6.257356356965984</v>
+        <v>6.238827318856497</v>
       </c>
       <c r="P6" t="n">
-        <v>282.5992261067452</v>
+        <v>282.6203679621141</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -16786,28 +16884,28 @@
         <v>0.1221</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1128910376943302</v>
+        <v>0.1087395549361866</v>
       </c>
       <c r="J7" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="K7" t="n">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01781496328455756</v>
+        <v>0.01676363409651227</v>
       </c>
       <c r="M7" t="n">
-        <v>4.688579248346998</v>
+        <v>4.678496583485679</v>
       </c>
       <c r="N7" t="n">
-        <v>35.8877839910541</v>
+        <v>35.72464079251517</v>
       </c>
       <c r="O7" t="n">
-        <v>5.990641367253935</v>
+        <v>5.977009351884534</v>
       </c>
       <c r="P7" t="n">
-        <v>295.6192043496058</v>
+        <v>295.6656207836872</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -16864,28 +16962,28 @@
         <v>0.1491</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1000566656078103</v>
+        <v>0.09948126780874272</v>
       </c>
       <c r="J8" t="n">
+        <v>322</v>
+      </c>
+      <c r="K8" t="n">
         <v>320</v>
       </c>
-      <c r="K8" t="n">
-        <v>318</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.01178147766691129</v>
+        <v>0.01181819076646873</v>
       </c>
       <c r="M8" t="n">
-        <v>5.331253854726874</v>
+        <v>5.300609241916055</v>
       </c>
       <c r="N8" t="n">
-        <v>42.99716448488849</v>
+        <v>42.72975387317705</v>
       </c>
       <c r="O8" t="n">
-        <v>6.557222314737277</v>
+        <v>6.536799971941703</v>
       </c>
       <c r="P8" t="n">
-        <v>297.4866595381953</v>
+        <v>297.4930889654049</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -16942,28 +17040,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1878792917160581</v>
+        <v>0.1844616382678989</v>
       </c>
       <c r="J9" t="n">
+        <v>322</v>
+      </c>
+      <c r="K9" t="n">
         <v>320</v>
       </c>
-      <c r="K9" t="n">
-        <v>318</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.04965295058018271</v>
+        <v>0.04857003971670737</v>
       </c>
       <c r="M9" t="n">
-        <v>4.552006795851972</v>
+        <v>4.539454314829655</v>
       </c>
       <c r="N9" t="n">
-        <v>34.5931043749238</v>
+        <v>34.41774375650476</v>
       </c>
       <c r="O9" t="n">
-        <v>5.88159029301802</v>
+        <v>5.866663767125637</v>
       </c>
       <c r="P9" t="n">
-        <v>300.5312457932789</v>
+        <v>300.5694393536296</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -17020,28 +17118,28 @@
         <v>0.0621</v>
       </c>
       <c r="I10" t="n">
-        <v>0.01430858018790318</v>
+        <v>0.0188554163537167</v>
       </c>
       <c r="J10" t="n">
+        <v>322</v>
+      </c>
+      <c r="K10" t="n">
         <v>320</v>
       </c>
-      <c r="K10" t="n">
-        <v>318</v>
-      </c>
       <c r="L10" t="n">
-        <v>0.0001391161995267787</v>
+        <v>0.0002448969624085917</v>
       </c>
       <c r="M10" t="n">
-        <v>6.472611591691011</v>
+        <v>6.457855952911731</v>
       </c>
       <c r="N10" t="n">
-        <v>75.3441427910802</v>
+        <v>74.94529856234517</v>
       </c>
       <c r="O10" t="n">
-        <v>8.680100390610709</v>
+        <v>8.657095272800523</v>
       </c>
       <c r="P10" t="n">
-        <v>306.0558163584412</v>
+        <v>306.0050029247695</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -17079,7 +17177,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K321"/>
+  <dimension ref="A1:K323"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35331,6 +35429,120 @@
         </is>
       </c>
     </row>
+    <row r="322">
+      <c r="A322" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:11:24+00:00</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>-35.560158364631576,174.50866959670833</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>-35.56069448197311,174.50789181125816</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>-35.561478937549005,174.50752543779856</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>-35.56228691200469,174.50726175647213</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>-35.563121965929945,174.50720570017748</t>
+        </is>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>-35.56402632691062,174.5074245241068</t>
+        </is>
+      </c>
+      <c r="H322" t="inlineStr">
+        <is>
+          <t>-35.564815939143195,174.50803917402746</t>
+        </is>
+      </c>
+      <c r="I322" t="inlineStr">
+        <is>
+          <t>-35.56542300346758,174.50884463909162</t>
+        </is>
+      </c>
+      <c r="J322" t="inlineStr">
+        <is>
+          <t>-35.56570735941588,174.5097566593995</t>
+        </is>
+      </c>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>-35.56016275538522,174.50867872293855</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>-35.560693398599234,174.5078891439729</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>-35.56148136420204,174.50753502767728</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>-35.56228620787139,174.5072563081065</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>-35.5631219678883,174.5072060311378</t>
+        </is>
+      </c>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>-35.56402452355673,174.5074312310582</t>
+        </is>
+      </c>
+      <c r="H323" t="inlineStr">
+        <is>
+          <t>-35.56481409611669,174.5080420318541</t>
+        </is>
+      </c>
+      <c r="I323" t="inlineStr">
+        <is>
+          <t>-35.56542070642313,174.5088465868633</t>
+        </is>
+      </c>
+      <c r="J323" t="inlineStr">
+        <is>
+          <t>-35.56570850789528,174.50975601908848</t>
+        </is>
+      </c>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
